--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:38:22+00:00</t>
+    <t>2026-08-28T12:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:52:33+00:00</t>
+    <t>2026-08-31T10:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:02:50+00:00</t>
+    <t>2026-09-01T06:51:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T06:51:10+00:00</t>
+    <t>2026-09-01T11:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:42:45+00:00</t>
+    <t>2026-09-01T12:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:48:31+00:00</t>
+    <t>2026-09-01T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:57:21+00:00</t>
+    <t>2026-09-03T13:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:31:10+00:00</t>
+    <t>2026-09-07T04:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T04:47:29+00:00</t>
+    <t>2026-09-07T06:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T06:52:33+00:00</t>
+    <t>2026-09-07T07:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:43:01+00:00</t>
+    <t>2026-09-07T07:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:56:25+00:00</t>
+    <t>2026-09-07T09:23:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:23:06+00:00</t>
+    <t>2026-09-07T10:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:17:45+00:00</t>
+    <t>2026-09-07T10:50:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:50:55+00:00</t>
+    <t>2026-09-08T06:03:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:03:03+00:00</t>
+    <t>2026-09-08T06:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:16:43+00:00</t>
+    <t>2026-09-08T06:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:28:20+00:00</t>
+    <t>2026-09-08T06:46:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:46:13+00:00</t>
+    <t>2026-09-08T10:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:19:13+00:00</t>
+    <t>2026-09-08T10:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:46:31+00:00</t>
+    <t>2026-09-08T11:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:50:41+00:00</t>
+    <t>2026-09-08T12:56:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:56:54+00:00</t>
+    <t>2026-09-09T04:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T04:29:28+00:00</t>
+    <t>2026-09-09T07:41:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T07:41:46+00:00</t>
+    <t>2026-09-09T08:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:03:40+00:00</t>
+    <t>2026-09-09T09:18:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:18:29+00:00</t>
+    <t>2026-09-09T14:48:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:48:33+00:00</t>
+    <t>2026-09-10T08:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:40:11+00:00</t>
+    <t>2026-09-10T09:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:01:10+00:00</t>
+    <t>2026-09-10T09:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:35:03+00:00</t>
+    <t>2026-09-10T09:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:50:09+00:00</t>
+    <t>2026-09-10T10:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:02:23+00:00</t>
+    <t>2026-09-10T11:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:15:10+00:00</t>
+    <t>2026-09-10T11:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:24:50+00:00</t>
+    <t>2026-09-10T11:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:47:23+00:00</t>
+    <t>2026-09-10T14:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:22:40+00:00</t>
+    <t>2026-09-11T07:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:57:50+00:00</t>
+    <t>2026-09-11T08:25:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
